--- a/AAII_Financials/Yearly/ELLO_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/ELLO_YR_FIN.xlsx
@@ -1251,7 +1251,7 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-4800</v>
+        <v>-5500</v>
       </c>
       <c r="E20" s="3">
         <v>-4400</v>
@@ -1302,7 +1302,7 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>26000</v>
+        <v>26600</v>
       </c>
       <c r="E21" s="3">
         <v>18800</v>
@@ -1863,7 +1863,7 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>4800</v>
+        <v>5500</v>
       </c>
       <c r="E32" s="3">
         <v>4400</v>
@@ -3026,7 +3026,7 @@
         <v>10800</v>
       </c>
       <c r="E59" s="3">
-        <v>4900</v>
+        <v>5500</v>
       </c>
       <c r="F59" s="3">
         <v>25500</v>
@@ -4093,7 +4093,7 @@
         <v>19400</v>
       </c>
       <c r="E83" s="3">
-        <v>16500</v>
+        <v>16400</v>
       </c>
       <c r="F83" s="3">
         <v>17700</v>
